--- a/uat/inputs/missing_required_column.xlsx
+++ b/uat/inputs/missing_required_column.xlsx
@@ -477,7 +477,7 @@
       <c r="C2" s="2" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>No model data column exists.</t>
+          <t>No input_data column exists.</t>
         </is>
       </c>
     </row>
